--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,60 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>201</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UI/Screens/ErrorDialog.prefab</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>202</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UI/Screens/Loading.prefab</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>203</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UI/Screens/Toast.prefab</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,6 +589,60 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>204</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UI/Screens/BaselineA.prefab</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>205</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UI/Screens/BaselineB.prefab</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>206</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UI/Screens/Dialog.prefab</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,65 +537,85 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>201</v>
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>UI.Page_Login</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UI/Screens/ErrorDialog.prefab</t>
+          <t>UI/Screens/Page_Login.prefab</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>202</v>
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UI.Page_Lobby</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UI/Screens/Loading.prefab</t>
+          <t>UI/Screens/Page_Lobby.prefab</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>203</v>
+        <v>13</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UI.Page_Room</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UI/Screens/Toast.prefab</t>
+          <t>UI/Screens/Page_Room.prefab</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>204</v>
+        <v>14</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UI.Page_Result</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UI/Screens/BaselineA.prefab</t>
+          <t>UI/Screens/Page_Result.prefab</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -609,15 +629,20 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>205</v>
+        <v>15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UI.Page_Settings</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UI/Screens/BaselineB.prefab</t>
+          <t>UI/Screens/Page_Settings.prefab</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -627,17 +652,107 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
+        <v>201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UI/Screens/Dialog.prefab</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>202</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UI/Screens/Loading.prefab</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>203</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>UI/Screens/Toast.prefab</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>204</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UI/Screens/BaselineA.prefab</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>205</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UI/Screens/BaselineB.prefab</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
         <v>206</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>UI/Screens/Dialog.prefab</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>false</t>
         </is>

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UI/Screens/UIMain.prefab</t>
+          <t>ShareResource/UI/Screens/UIMain.prefab</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UI/Screens/Page_Login.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Login.prefab</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -569,7 +569,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UI/Screens/Page_Lobby.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Lobby.prefab</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UI/Screens/Page_Room.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Room.prefab</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UI/Screens/Page_Result.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Result.prefab</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UI/Screens/Page_Settings.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Settings.prefab</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UI/Screens/Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Dialog.prefab</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UI/Screens/Loading.prefab</t>
+          <t>ShareResource/UI/Screens/Loading.prefab</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UI/Screens/Toast.prefab</t>
+          <t>ShareResource/UI/Screens/Toast.prefab</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UI/Screens/BaselineA.prefab</t>
+          <t>ShareResource/UI/Screens/BaselineA.prefab</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -728,7 +728,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UI/Screens/BaselineB.prefab</t>
+          <t>ShareResource/UI/Screens/BaselineB.prefab</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UI/Screens/Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Dialog.prefab</t>
         </is>
       </c>
       <c r="E15" t="n">

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Loading.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Loading.prefab</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Toast.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Toast.prefab</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/BaselineA.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_BaselineA.prefab</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -728,7 +728,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/BaselineB.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_BaselineB.prefab</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
         </is>
       </c>
       <c r="E15" t="n">

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,29 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UI.Page_Records</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ShareResource/UI/Screens/Page_Records.prefab</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UI.UIMain</t>
+          <t>UI.Page_Login</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/UIMain.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Login.prefab</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -537,16 +537,16 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UI.Page_Login</t>
+          <t>UI.Page_Lobby</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Page_Login.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Lobby.prefab</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -560,16 +560,16 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UI.Page_Lobby</t>
+          <t>UI.Page_Room</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Page_Lobby.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Room.prefab</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -583,16 +583,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UI.Page_Room</t>
+          <t>UI.Page_Result</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Page_Room.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Result.prefab</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -606,20 +606,20 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UI.Page_Result</t>
+          <t>UI.Page_Settings</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Page_Result.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Settings.prefab</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -629,34 +629,29 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>15</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>UI.Page_Settings</t>
-        </is>
+        <v>201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Page_Settings.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Loading.prefab</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -670,11 +665,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_Loading.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Toast.prefab</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -688,33 +683,33 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_Toast.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_BaselineA.prefab</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_BaselineA.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_BaselineB.prefab</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -724,58 +719,40 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_BaselineB.prefab</t>
+          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>206</v>
+        <v>16</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UI.Page_Records</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ShareResource/UI/Screens/Tmp_Dialog.prefab</t>
+          <t>ShareResource/UI/Screens/Page_Records.prefab</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>UI.Page_Records</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ShareResource/UI/Screens/Page_Records.prefab</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>true</t>
         </is>
